--- a/planilha_vp.xlsx
+++ b/planilha_vp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hdusa\Documents\Github\vp-gps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9565C3C-FEE5-423C-A756-69A66270846B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD38982-51E2-4C83-A0F0-2CA72EF9FC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Escala VP" sheetId="1" r:id="rId1"/>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>PMMG29397</t>
-  </si>
-  <si>
-    <t>SGT ALICE</t>
   </si>
   <si>
     <t>PMMG29378</t>
@@ -506,6 +503,9 @@
   <si>
     <t>VERUS</t>
   </si>
+  <si>
+    <t>SGT ALICE</t>
+  </si>
 </sst>
 </file>
 
@@ -646,7 +646,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -941,13 +941,13 @@
         <v>46132</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>8</v>
@@ -989,13 +989,13 @@
         <v>46132</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>8</v>
@@ -1037,13 +1037,13 @@
         <v>46132</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>15</v>
@@ -1085,13 +1085,13 @@
         <v>46132</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>15</v>
@@ -1131,13 +1131,13 @@
         <v>46132</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>20</v>
@@ -1175,13 +1175,13 @@
         <v>46132</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>20</v>
@@ -1221,13 +1221,13 @@
         <v>46133</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>8</v>
@@ -1265,13 +1265,13 @@
         <v>46133</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>8</v>
@@ -1309,13 +1309,13 @@
         <v>46133</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>15</v>
@@ -1355,13 +1355,13 @@
         <v>46133</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>15</v>
@@ -1399,19 +1399,19 @@
         <v>46133</v>
       </c>
       <c r="B12" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" s="6">
         <v>11</v>
@@ -1443,19 +1443,19 @@
         <v>46133</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G13" s="6">
         <v>12</v>
@@ -1487,19 +1487,19 @@
         <v>46134</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G14" s="6">
         <v>13</v>
@@ -1531,13 +1531,13 @@
         <v>46134</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>8</v>
@@ -1577,19 +1577,19 @@
         <v>46134</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G16" s="6">
         <v>15</v>
@@ -1623,19 +1623,19 @@
         <v>46134</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" s="6">
         <v>16</v>
@@ -1667,19 +1667,19 @@
         <v>46134</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18" s="6">
         <v>17</v>
@@ -1711,13 +1711,13 @@
         <v>46134</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>20</v>
@@ -1757,19 +1757,19 @@
         <v>46135</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G20" s="6">
         <v>19</v>
@@ -1801,19 +1801,19 @@
         <v>46135</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" s="6">
         <v>20</v>
@@ -1845,19 +1845,19 @@
         <v>46135</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G22" s="6">
         <v>21</v>
@@ -1889,19 +1889,19 @@
         <v>46135</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G23" s="6">
         <v>22</v>
@@ -1933,19 +1933,19 @@
         <v>46135</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G24" s="6">
         <v>23</v>
@@ -1979,19 +1979,19 @@
         <v>46135</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G25" s="6">
         <v>24</v>
@@ -2025,19 +2025,19 @@
         <v>46136</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G26" s="6">
         <v>25</v>
@@ -2069,19 +2069,19 @@
         <v>46136</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G27" s="6">
         <v>26</v>
@@ -2113,19 +2113,19 @@
         <v>46136</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G28" s="6">
         <v>27</v>
@@ -2159,19 +2159,19 @@
         <v>46136</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G29" s="6">
         <v>28</v>
@@ -2205,19 +2205,19 @@
         <v>46136</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G30" s="6">
         <v>29</v>
@@ -2249,19 +2249,19 @@
         <v>46136</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G31" s="6">
         <v>30</v>
@@ -2293,13 +2293,13 @@
         <v>46137</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
@@ -2337,13 +2337,13 @@
         <v>46137</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>8</v>
@@ -2383,19 +2383,19 @@
         <v>46137</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G34" s="6">
         <v>33</v>
@@ -2429,13 +2429,13 @@
         <v>46137</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>15</v>
@@ -2473,19 +2473,19 @@
         <v>46137</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G36" s="6">
         <v>35</v>
@@ -2517,13 +2517,13 @@
         <v>46137</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>20</v>
@@ -2563,19 +2563,19 @@
         <v>46138</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G38" s="6">
         <v>37</v>
@@ -2607,13 +2607,13 @@
         <v>46138</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>8</v>
@@ -2653,19 +2653,19 @@
         <v>46138</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G40" s="6">
         <v>39</v>
@@ -2699,19 +2699,19 @@
         <v>46138</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G41" s="6">
         <v>40</v>
@@ -2743,19 +2743,19 @@
         <v>46138</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G42" s="6">
         <v>41</v>
@@ -2787,13 +2787,13 @@
         <v>46138</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>20</v>
@@ -2833,19 +2833,19 @@
         <v>46139</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G44" s="6">
         <v>43</v>
@@ -2877,19 +2877,19 @@
         <v>46139</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G45" s="6">
         <v>44</v>
@@ -2921,19 +2921,19 @@
         <v>46139</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G46" s="6">
         <v>45</v>
@@ -2967,13 +2967,13 @@
         <v>46139</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>15</v>
@@ -3011,19 +3011,19 @@
         <v>46139</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G48" s="6">
         <v>47</v>
@@ -3057,19 +3057,19 @@
         <v>46139</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G49" s="6">
         <v>48</v>
@@ -3103,19 +3103,19 @@
         <v>46140</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G50" s="6">
         <v>49</v>
@@ -3149,19 +3149,19 @@
         <v>46140</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G51" s="6">
         <v>50</v>
@@ -3195,19 +3195,19 @@
         <v>46140</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G52" s="6">
         <v>51</v>
@@ -3239,19 +3239,19 @@
         <v>46140</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G53" s="6">
         <v>52</v>
@@ -3283,19 +3283,19 @@
         <v>46140</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G54" s="6">
         <v>53</v>
@@ -3327,19 +3327,19 @@
         <v>46140</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G55" s="6">
         <v>54</v>
@@ -3371,19 +3371,19 @@
         <v>46141</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G56" s="6">
         <v>55</v>
@@ -3415,19 +3415,19 @@
         <v>46141</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G57" s="6">
         <v>56</v>
@@ -3459,19 +3459,19 @@
         <v>46141</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G58" s="6">
         <v>57</v>
@@ -3503,19 +3503,19 @@
         <v>46141</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G59" s="6">
         <v>58</v>
@@ -3547,19 +3547,19 @@
         <v>46141</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G60" s="6">
         <v>59</v>
@@ -3593,19 +3593,19 @@
         <v>46141</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G61" s="6">
         <v>60</v>
@@ -3639,19 +3639,19 @@
         <v>46142</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G62" s="6">
         <v>61</v>
@@ -3685,13 +3685,13 @@
         <v>46142</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>8</v>
@@ -3731,19 +3731,19 @@
         <v>46142</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G64" s="6">
         <v>63</v>
@@ -3777,26 +3777,26 @@
         <v>46142</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G65" s="6">
         <v>64</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
@@ -3823,26 +3823,26 @@
         <v>46142</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G66" s="6">
         <v>65</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
@@ -3869,26 +3869,26 @@
         <v>46142</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G67" s="6">
         <v>66</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
@@ -3915,13 +3915,13 @@
         <v>46143</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>8</v>
@@ -3959,13 +3959,13 @@
         <v>46143</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>8</v>
@@ -4005,13 +4005,13 @@
         <v>46143</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>15</v>
@@ -4049,26 +4049,26 @@
         <v>46143</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G71" s="6">
         <v>70</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
@@ -4095,13 +4095,13 @@
         <v>46143</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>20</v>
@@ -4139,13 +4139,13 @@
         <v>46143</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>20</v>
@@ -4185,19 +4185,19 @@
         <v>46144</v>
       </c>
       <c r="B74" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="D74" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G74" s="6">
         <v>73</v>
@@ -4229,19 +4229,19 @@
         <v>46144</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G75" s="6">
         <v>74</v>
@@ -4273,19 +4273,19 @@
         <v>46144</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G76" s="6">
         <v>75</v>
@@ -4317,19 +4317,19 @@
         <v>46144</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G77" s="6">
         <v>76</v>
@@ -4361,19 +4361,19 @@
         <v>46144</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G78" s="6">
         <v>77</v>
@@ -4407,26 +4407,26 @@
         <v>46144</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F79" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G79" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="H79" s="8"/>
       <c r="I79" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
@@ -4453,19 +4453,19 @@
         <v>46145</v>
       </c>
       <c r="B80" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="D80" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G80" s="6">
         <v>79</v>
@@ -4497,19 +4497,19 @@
         <v>46145</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G81" s="6">
         <v>80</v>
@@ -4541,19 +4541,19 @@
         <v>46145</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G82" s="6">
         <v>81</v>
@@ -4585,19 +4585,19 @@
         <v>46145</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G83" s="6">
         <v>82</v>
@@ -4629,19 +4629,19 @@
         <v>46145</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G84" s="6">
         <v>83</v>
@@ -4675,19 +4675,19 @@
         <v>46145</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G85" s="6">
         <v>84</v>
@@ -4719,19 +4719,19 @@
         <v>46146</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G86" s="6">
         <v>85</v>
@@ -4765,13 +4765,13 @@
         <v>46146</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>8</v>
@@ -4811,19 +4811,19 @@
         <v>46146</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G88" s="6">
         <v>87</v>
@@ -4857,19 +4857,19 @@
         <v>46146</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G89" s="6">
         <v>88</v>
@@ -4903,19 +4903,19 @@
         <v>46146</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G90" s="6">
         <v>89</v>
@@ -4947,26 +4947,26 @@
         <v>46146</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G91" s="6">
         <v>90</v>
       </c>
       <c r="H91" s="8"/>
       <c r="I91" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
@@ -4993,19 +4993,19 @@
         <v>46147</v>
       </c>
       <c r="B92" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="D92" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G92" s="6">
         <v>91</v>
@@ -5037,19 +5037,19 @@
         <v>46147</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G93" s="6">
         <v>92</v>
@@ -5081,19 +5081,19 @@
         <v>46147</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G94" s="6">
         <v>93</v>
@@ -5102,7 +5102,7 @@
         <v>13</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
@@ -5129,19 +5129,19 @@
         <v>46147</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G95" s="6">
         <v>94</v>
@@ -5173,28 +5173,28 @@
         <v>46147</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F96" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G96" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="G96" s="6" t="s">
+      <c r="H96" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="I96" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
@@ -5221,19 +5221,19 @@
         <v>46147</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G97" s="6">
         <v>96</v>

--- a/planilha_vp.xlsx
+++ b/planilha_vp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hdusa\Documents\Github\vp-gps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD38982-51E2-4C83-A0F0-2CA72EF9FC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E44CB8D-D56D-44E2-A828-E566DDD8F668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="158">
   <si>
     <t>Data</t>
   </si>
@@ -229,9 +229,6 @@
   </si>
   <si>
     <t>PMMG29400</t>
-  </si>
-  <si>
-    <t>SGT ANDRESSA</t>
   </si>
   <si>
     <t>PMMG29376(29397)</t>
@@ -895,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -941,13 +938,13 @@
         <v>46132</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>8</v>
@@ -989,13 +986,13 @@
         <v>46132</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>8</v>
@@ -1037,13 +1034,13 @@
         <v>46132</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>15</v>
@@ -1085,13 +1082,13 @@
         <v>46132</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>15</v>
@@ -1131,13 +1128,13 @@
         <v>46132</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>20</v>
@@ -1175,13 +1172,13 @@
         <v>46132</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>20</v>
@@ -1221,13 +1218,13 @@
         <v>46133</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>8</v>
@@ -1265,13 +1262,13 @@
         <v>46133</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>8</v>
@@ -1309,13 +1306,13 @@
         <v>46133</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>15</v>
@@ -1355,13 +1352,13 @@
         <v>46133</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>15</v>
@@ -1399,13 +1396,13 @@
         <v>46133</v>
       </c>
       <c r="B12" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>20</v>
@@ -1443,13 +1440,13 @@
         <v>46133</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>20</v>
@@ -1487,13 +1484,13 @@
         <v>46134</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1531,13 +1528,13 @@
         <v>46134</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>8</v>
@@ -1577,13 +1574,13 @@
         <v>46134</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>15</v>
@@ -1623,13 +1620,13 @@
         <v>46134</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>15</v>
@@ -1667,13 +1664,13 @@
         <v>46134</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>20</v>
@@ -1711,13 +1708,13 @@
         <v>46134</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>20</v>
@@ -1757,13 +1754,13 @@
         <v>46135</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
@@ -1801,13 +1798,13 @@
         <v>46135</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>8</v>
@@ -1845,13 +1842,13 @@
         <v>46135</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>15</v>
@@ -1889,13 +1886,13 @@
         <v>46135</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>15</v>
@@ -1933,13 +1930,13 @@
         <v>46135</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>20</v>
@@ -1979,13 +1976,13 @@
         <v>46135</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>20</v>
@@ -2025,13 +2022,13 @@
         <v>46136</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>8</v>
@@ -2069,13 +2066,13 @@
         <v>46136</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>8</v>
@@ -2113,13 +2110,13 @@
         <v>46136</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>15</v>
@@ -2159,13 +2156,13 @@
         <v>46136</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>15</v>
@@ -2205,13 +2202,13 @@
         <v>46136</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>20</v>
@@ -2249,13 +2246,13 @@
         <v>46136</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>20</v>
@@ -2293,13 +2290,13 @@
         <v>46137</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
@@ -2337,13 +2334,13 @@
         <v>46137</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>8</v>
@@ -2383,13 +2380,13 @@
         <v>46137</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>15</v>
@@ -2429,13 +2426,13 @@
         <v>46137</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>15</v>
@@ -2473,13 +2470,13 @@
         <v>46137</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>20</v>
@@ -2517,13 +2514,13 @@
         <v>46137</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>20</v>
@@ -2563,13 +2560,13 @@
         <v>46138</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>8</v>
@@ -2607,13 +2604,13 @@
         <v>46138</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>8</v>
@@ -2653,13 +2650,13 @@
         <v>46138</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>15</v>
@@ -2699,13 +2696,13 @@
         <v>46138</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>15</v>
@@ -2743,13 +2740,13 @@
         <v>46138</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>20</v>
@@ -2787,13 +2784,13 @@
         <v>46138</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>20</v>
@@ -2833,13 +2830,13 @@
         <v>46139</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>8</v>
@@ -2877,13 +2874,13 @@
         <v>46139</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
@@ -2921,13 +2918,13 @@
         <v>46139</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>15</v>
@@ -2967,13 +2964,13 @@
         <v>46139</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>15</v>
@@ -3011,13 +3008,13 @@
         <v>46139</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>20</v>
@@ -3057,13 +3054,13 @@
         <v>46139</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>20</v>
@@ -3103,13 +3100,13 @@
         <v>46140</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>8</v>
@@ -3149,13 +3146,13 @@
         <v>46140</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>8</v>
@@ -3195,13 +3192,13 @@
         <v>46140</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>15</v>
@@ -3239,13 +3236,13 @@
         <v>46140</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>15</v>
@@ -3283,13 +3280,13 @@
         <v>46140</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>20</v>
@@ -3327,13 +3324,13 @@
         <v>46140</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>20</v>
@@ -3371,13 +3368,13 @@
         <v>46141</v>
       </c>
       <c r="B56" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="D56" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>8</v>
@@ -3415,13 +3412,13 @@
         <v>46141</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>8</v>
@@ -3459,19 +3456,19 @@
         <v>46141</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G58" s="6">
         <v>57</v>
@@ -3503,13 +3500,13 @@
         <v>46141</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>15</v>
@@ -3547,13 +3544,13 @@
         <v>46141</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>20</v>
@@ -3593,13 +3590,13 @@
         <v>46141</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>20</v>
@@ -3639,19 +3636,19 @@
         <v>46142</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G62" s="6">
         <v>61</v>
@@ -3685,13 +3682,13 @@
         <v>46142</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>8</v>
@@ -3731,19 +3728,19 @@
         <v>46142</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G64" s="6">
         <v>63</v>
@@ -3777,26 +3774,26 @@
         <v>46142</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G65" s="6">
         <v>64</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
@@ -3823,26 +3820,26 @@
         <v>46142</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G66" s="6">
         <v>65</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
@@ -3869,26 +3866,26 @@
         <v>46142</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G67" s="6">
         <v>66</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
@@ -3915,13 +3912,13 @@
         <v>46143</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>8</v>
@@ -3959,13 +3956,13 @@
         <v>46143</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>8</v>
@@ -4005,13 +4002,13 @@
         <v>46143</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>15</v>
@@ -4049,13 +4046,13 @@
         <v>46143</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>15</v>
@@ -4068,7 +4065,7 @@
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
@@ -4095,13 +4092,13 @@
         <v>46143</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>20</v>
@@ -4139,13 +4136,13 @@
         <v>46143</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>20</v>
@@ -4185,19 +4182,19 @@
         <v>46144</v>
       </c>
       <c r="B74" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="D74" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G74" s="6">
         <v>73</v>
@@ -4229,19 +4226,19 @@
         <v>46144</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G75" s="6">
         <v>74</v>
@@ -4273,19 +4270,19 @@
         <v>46144</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G76" s="6">
         <v>75</v>
@@ -4317,19 +4314,19 @@
         <v>46144</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G77" s="6">
         <v>76</v>
@@ -4361,19 +4358,19 @@
         <v>46144</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G78" s="6">
         <v>77</v>
@@ -4407,26 +4404,26 @@
         <v>46144</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F79" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G79" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="H79" s="8"/>
       <c r="I79" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
@@ -4453,19 +4450,19 @@
         <v>46145</v>
       </c>
       <c r="B80" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="D80" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G80" s="6">
         <v>79</v>
@@ -4497,19 +4494,19 @@
         <v>46145</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G81" s="6">
         <v>80</v>
@@ -4541,19 +4538,19 @@
         <v>46145</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G82" s="6">
         <v>81</v>
@@ -4585,19 +4582,19 @@
         <v>46145</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G83" s="6">
         <v>82</v>
@@ -4629,19 +4626,19 @@
         <v>46145</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G84" s="6">
         <v>83</v>
@@ -4675,19 +4672,19 @@
         <v>46145</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G85" s="6">
         <v>84</v>
@@ -4719,19 +4716,19 @@
         <v>46146</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G86" s="6">
         <v>85</v>
@@ -4765,13 +4762,13 @@
         <v>46146</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>8</v>
@@ -4811,19 +4808,19 @@
         <v>46146</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G88" s="6">
         <v>87</v>
@@ -4857,13 +4854,13 @@
         <v>46146</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>15</v>
@@ -4903,19 +4900,19 @@
         <v>46146</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G90" s="6">
         <v>89</v>
@@ -4947,26 +4944,26 @@
         <v>46146</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G91" s="6">
         <v>90</v>
       </c>
       <c r="H91" s="8"/>
       <c r="I91" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
@@ -4993,19 +4990,19 @@
         <v>46147</v>
       </c>
       <c r="B92" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="D92" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G92" s="6">
         <v>91</v>
@@ -5037,19 +5034,19 @@
         <v>46147</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G93" s="6">
         <v>92</v>
@@ -5081,19 +5078,19 @@
         <v>46147</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G94" s="6">
         <v>93</v>
@@ -5102,7 +5099,7 @@
         <v>13</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
@@ -5129,19 +5126,19 @@
         <v>46147</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G95" s="6">
         <v>94</v>
@@ -5173,28 +5170,28 @@
         <v>46147</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F96" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G96" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="G96" s="6" t="s">
+      <c r="H96" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="I96" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
@@ -5221,19 +5218,19 @@
         <v>46147</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G97" s="6">
         <v>96</v>
